--- a/data/Heat map 4-1 Capacity Building.xlsx
+++ b/data/Heat map 4-1 Capacity Building.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2CD6BE5-9196-468B-9F6F-740B9731CB48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8705F90E-0B78-4D0E-A361-82055CC6C799}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{60C6FB9E-1B92-4818-B8F8-C10D82D4AFAC}"/>
   </bookViews>
@@ -139,9 +139,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -551,21 +553,9 @@
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="1" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -581,116 +571,128 @@
     <xf numFmtId="165" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1000,775 +1002,778 @@
   <cols>
     <col min="1" max="1" width="13.44140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.44140625" style="1" customWidth="1"/>
-    <col min="3" max="14" width="5" style="5" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="7.5546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="8" width="5" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="10" max="14" width="5" style="5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.109375" style="4" bestFit="1" customWidth="1"/>
     <col min="16" max="20" width="5" style="5" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="6.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="8.109375" style="3" bestFit="1" customWidth="1"/>
     <col min="22" max="26" width="5" style="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" s="2" customFormat="1" ht="15.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="18"/>
-      <c r="N1" s="18"/>
-      <c r="O1" s="18"/>
-      <c r="P1" s="18"/>
-      <c r="Q1" s="18"/>
-      <c r="R1" s="18"/>
-      <c r="S1" s="18"/>
-      <c r="T1" s="18"/>
-      <c r="U1" s="18"/>
-      <c r="V1" s="18"/>
-      <c r="W1" s="18"/>
-      <c r="X1" s="18"/>
-      <c r="Y1" s="18"/>
-      <c r="Z1" s="19"/>
-    </row>
-    <row r="2" spans="1:26" s="8" customFormat="1" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="16"/>
-      <c r="B2" s="49" t="s">
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="31"/>
+      <c r="N1" s="31"/>
+      <c r="O1" s="31"/>
+      <c r="P1" s="31"/>
+      <c r="Q1" s="31"/>
+      <c r="R1" s="31"/>
+      <c r="S1" s="31"/>
+      <c r="T1" s="31"/>
+      <c r="U1" s="31"/>
+      <c r="V1" s="31"/>
+      <c r="W1" s="31"/>
+      <c r="X1" s="31"/>
+      <c r="Y1" s="31"/>
+      <c r="Z1" s="32"/>
+    </row>
+    <row r="2" spans="1:26" s="6" customFormat="1" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="39"/>
+      <c r="B2" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="20" t="s">
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="J2" s="21"/>
-      <c r="K2" s="21"/>
-      <c r="L2" s="21"/>
-      <c r="M2" s="21"/>
-      <c r="N2" s="22"/>
-      <c r="O2" s="20" t="s">
+      <c r="J2" s="34"/>
+      <c r="K2" s="34"/>
+      <c r="L2" s="34"/>
+      <c r="M2" s="34"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="P2" s="21"/>
-      <c r="Q2" s="21"/>
-      <c r="R2" s="21"/>
-      <c r="S2" s="21"/>
-      <c r="T2" s="22"/>
-      <c r="U2" s="20" t="s">
+      <c r="P2" s="34"/>
+      <c r="Q2" s="34"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="34"/>
+      <c r="T2" s="35"/>
+      <c r="U2" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="V2" s="21"/>
-      <c r="W2" s="21"/>
-      <c r="X2" s="21"/>
-      <c r="Y2" s="21"/>
-      <c r="Z2" s="22"/>
+      <c r="V2" s="34"/>
+      <c r="W2" s="34"/>
+      <c r="X2" s="34"/>
+      <c r="Y2" s="34"/>
+      <c r="Z2" s="35"/>
     </row>
     <row r="3" spans="1:26" s="1" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="16"/>
-      <c r="B3" s="48"/>
-      <c r="C3" s="14" t="s">
+      <c r="A3" s="39"/>
+      <c r="B3" s="29"/>
+      <c r="C3" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="13" t="s">
+      <c r="H3" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="14" t="s">
+      <c r="I3" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="J3" s="12" t="s">
+      <c r="J3" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="K3" s="12" t="s">
+      <c r="K3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="L3" s="12" t="s">
+      <c r="L3" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="M3" s="12" t="s">
+      <c r="M3" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="N3" s="13" t="s">
+      <c r="N3" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="O3" s="11" t="s">
+      <c r="O3" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="P3" s="12" t="s">
+      <c r="P3" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="Q3" s="12" t="s">
+      <c r="Q3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="R3" s="12" t="s">
+      <c r="R3" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="S3" s="12" t="s">
+      <c r="S3" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="T3" s="12" t="s">
+      <c r="T3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="U3" s="15" t="s">
+      <c r="U3" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="V3" s="12" t="s">
+      <c r="V3" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="W3" s="12" t="s">
+      <c r="W3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="X3" s="12" t="s">
+      <c r="X3" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="Y3" s="12" t="s">
+      <c r="Y3" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="Z3" s="13" t="s">
+      <c r="Z3" s="9" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:26" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="33" t="s">
+      <c r="B4" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="37">
+      <c r="C4" s="41">
         <v>1</v>
       </c>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="39"/>
-      <c r="I4" s="37">
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="41">
         <v>1</v>
       </c>
-      <c r="J4" s="38"/>
-      <c r="K4" s="38"/>
-      <c r="L4" s="38"/>
-      <c r="M4" s="38"/>
-      <c r="N4" s="39"/>
-      <c r="O4" s="45">
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="20"/>
+      <c r="M4" s="20"/>
+      <c r="N4" s="21"/>
+      <c r="O4" s="48">
         <v>68</v>
       </c>
-      <c r="P4" s="38"/>
-      <c r="Q4" s="38"/>
-      <c r="R4" s="38"/>
-      <c r="S4" s="38"/>
-      <c r="T4" s="39"/>
-      <c r="U4" s="45">
+      <c r="P4" s="20"/>
+      <c r="Q4" s="20"/>
+      <c r="R4" s="20"/>
+      <c r="S4" s="20"/>
+      <c r="T4" s="21"/>
+      <c r="U4" s="48">
         <v>184</v>
       </c>
-      <c r="V4" s="38"/>
-      <c r="W4" s="38"/>
-      <c r="X4" s="38"/>
-      <c r="Y4" s="38"/>
-      <c r="Z4" s="39"/>
+      <c r="V4" s="20"/>
+      <c r="W4" s="20"/>
+      <c r="X4" s="20"/>
+      <c r="Y4" s="20"/>
+      <c r="Z4" s="21"/>
     </row>
     <row r="5" spans="1:26" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="25"/>
-      <c r="B5" s="33" t="s">
+      <c r="A5" s="37"/>
+      <c r="B5" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="40">
+      <c r="C5" s="42">
         <v>24</v>
       </c>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="36"/>
-      <c r="G5" s="36"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="40">
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="22"/>
+      <c r="I5" s="42">
         <v>28</v>
       </c>
-      <c r="J5" s="36"/>
-      <c r="K5" s="36"/>
-      <c r="L5" s="36"/>
-      <c r="M5" s="36"/>
-      <c r="N5" s="41"/>
-      <c r="O5" s="46">
+      <c r="J5" s="19"/>
+      <c r="K5" s="19"/>
+      <c r="L5" s="19"/>
+      <c r="M5" s="19"/>
+      <c r="N5" s="22"/>
+      <c r="O5" s="49">
         <v>108</v>
       </c>
-      <c r="P5" s="36"/>
-      <c r="Q5" s="36"/>
-      <c r="R5" s="36"/>
-      <c r="S5" s="36"/>
-      <c r="T5" s="41"/>
-      <c r="U5" s="46">
+      <c r="P5" s="19"/>
+      <c r="Q5" s="19"/>
+      <c r="R5" s="19"/>
+      <c r="S5" s="19"/>
+      <c r="T5" s="22"/>
+      <c r="U5" s="49">
         <v>214</v>
       </c>
-      <c r="V5" s="36"/>
-      <c r="W5" s="36"/>
-      <c r="X5" s="36"/>
-      <c r="Y5" s="36"/>
-      <c r="Z5" s="41"/>
+      <c r="V5" s="19"/>
+      <c r="W5" s="19"/>
+      <c r="X5" s="19"/>
+      <c r="Y5" s="19"/>
+      <c r="Z5" s="22"/>
     </row>
     <row r="6" spans="1:26" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="25"/>
-      <c r="B6" s="33" t="s">
+      <c r="A6" s="37"/>
+      <c r="B6" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="40">
+      <c r="C6" s="42">
         <v>26</v>
       </c>
-      <c r="D6" s="36"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="36"/>
-      <c r="G6" s="36"/>
-      <c r="H6" s="41"/>
-      <c r="I6" s="40">
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="42">
         <v>19</v>
       </c>
-      <c r="J6" s="36"/>
-      <c r="K6" s="36"/>
-      <c r="L6" s="36"/>
-      <c r="M6" s="36"/>
-      <c r="N6" s="41"/>
-      <c r="O6" s="46">
+      <c r="J6" s="19"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="19"/>
+      <c r="M6" s="19"/>
+      <c r="N6" s="22"/>
+      <c r="O6" s="49">
         <v>5</v>
       </c>
-      <c r="P6" s="36"/>
-      <c r="Q6" s="36"/>
-      <c r="R6" s="36"/>
-      <c r="S6" s="36"/>
-      <c r="T6" s="41"/>
-      <c r="U6" s="46">
+      <c r="P6" s="19"/>
+      <c r="Q6" s="19"/>
+      <c r="R6" s="19"/>
+      <c r="S6" s="19"/>
+      <c r="T6" s="22"/>
+      <c r="U6" s="49">
         <v>113</v>
       </c>
-      <c r="V6" s="36"/>
-      <c r="W6" s="36"/>
-      <c r="X6" s="36"/>
-      <c r="Y6" s="36"/>
-      <c r="Z6" s="41"/>
+      <c r="V6" s="19"/>
+      <c r="W6" s="19"/>
+      <c r="X6" s="19"/>
+      <c r="Y6" s="19"/>
+      <c r="Z6" s="22"/>
     </row>
     <row r="7" spans="1:26" s="1" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="26"/>
-      <c r="B7" s="34" t="s">
+      <c r="A7" s="38"/>
+      <c r="B7" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="40">
+      <c r="C7" s="42">
         <v>5</v>
       </c>
-      <c r="D7" s="36"/>
-      <c r="E7" s="36"/>
-      <c r="F7" s="36"/>
-      <c r="G7" s="36"/>
-      <c r="H7" s="41"/>
-      <c r="I7" s="40">
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="22"/>
+      <c r="I7" s="42">
         <v>7</v>
       </c>
-      <c r="J7" s="36"/>
-      <c r="K7" s="36"/>
-      <c r="L7" s="36"/>
-      <c r="M7" s="36"/>
-      <c r="N7" s="41"/>
-      <c r="O7" s="46">
+      <c r="J7" s="19"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="19"/>
+      <c r="M7" s="19"/>
+      <c r="N7" s="22"/>
+      <c r="O7" s="49">
         <v>2247</v>
       </c>
-      <c r="P7" s="36"/>
-      <c r="Q7" s="36"/>
-      <c r="R7" s="36"/>
-      <c r="S7" s="36"/>
-      <c r="T7" s="41"/>
-      <c r="U7" s="46">
+      <c r="P7" s="19"/>
+      <c r="Q7" s="19"/>
+      <c r="R7" s="19"/>
+      <c r="S7" s="19"/>
+      <c r="T7" s="22"/>
+      <c r="U7" s="49">
         <v>309</v>
       </c>
-      <c r="V7" s="36"/>
-      <c r="W7" s="36"/>
-      <c r="X7" s="36"/>
-      <c r="Y7" s="36"/>
-      <c r="Z7" s="41"/>
+      <c r="V7" s="19"/>
+      <c r="W7" s="19"/>
+      <c r="X7" s="19"/>
+      <c r="Y7" s="19"/>
+      <c r="Z7" s="22"/>
     </row>
     <row r="8" spans="1:26" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="24" t="s">
+      <c r="A8" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="35" t="s">
+      <c r="B8" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="40">
+      <c r="C8" s="42">
         <v>9</v>
       </c>
-      <c r="D8" s="36"/>
-      <c r="E8" s="36"/>
-      <c r="F8" s="36"/>
-      <c r="G8" s="36"/>
-      <c r="H8" s="41"/>
-      <c r="I8" s="40">
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="22"/>
+      <c r="I8" s="42">
         <v>9</v>
       </c>
-      <c r="J8" s="36"/>
-      <c r="K8" s="36"/>
-      <c r="L8" s="36"/>
-      <c r="M8" s="36"/>
-      <c r="N8" s="41"/>
-      <c r="O8" s="46">
+      <c r="J8" s="19"/>
+      <c r="K8" s="19"/>
+      <c r="L8" s="19"/>
+      <c r="M8" s="19"/>
+      <c r="N8" s="22"/>
+      <c r="O8" s="49">
         <v>102</v>
       </c>
-      <c r="P8" s="36"/>
-      <c r="Q8" s="36"/>
-      <c r="R8" s="36"/>
-      <c r="S8" s="36"/>
-      <c r="T8" s="41"/>
-      <c r="U8" s="46">
+      <c r="P8" s="19"/>
+      <c r="Q8" s="19"/>
+      <c r="R8" s="19"/>
+      <c r="S8" s="19"/>
+      <c r="T8" s="22"/>
+      <c r="U8" s="49">
         <v>10</v>
       </c>
-      <c r="V8" s="36"/>
-      <c r="W8" s="36"/>
-      <c r="X8" s="36"/>
-      <c r="Y8" s="36"/>
-      <c r="Z8" s="41"/>
+      <c r="V8" s="19"/>
+      <c r="W8" s="19"/>
+      <c r="X8" s="19"/>
+      <c r="Y8" s="19"/>
+      <c r="Z8" s="22"/>
     </row>
     <row r="9" spans="1:26" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="25"/>
-      <c r="B9" s="33" t="s">
+      <c r="A9" s="37"/>
+      <c r="B9" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="40">
+      <c r="C9" s="42">
         <v>22</v>
       </c>
-      <c r="D9" s="36"/>
-      <c r="E9" s="36"/>
-      <c r="F9" s="36"/>
-      <c r="G9" s="36"/>
-      <c r="H9" s="41"/>
-      <c r="I9" s="40">
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="42">
         <v>14</v>
       </c>
-      <c r="J9" s="36"/>
-      <c r="K9" s="36"/>
-      <c r="L9" s="36"/>
-      <c r="M9" s="36"/>
-      <c r="N9" s="41"/>
-      <c r="O9" s="46">
+      <c r="J9" s="19"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="22"/>
+      <c r="O9" s="49">
         <v>3185</v>
       </c>
-      <c r="P9" s="36"/>
-      <c r="Q9" s="36"/>
-      <c r="R9" s="36"/>
-      <c r="S9" s="36"/>
-      <c r="T9" s="41"/>
-      <c r="U9" s="46">
+      <c r="P9" s="19"/>
+      <c r="Q9" s="19"/>
+      <c r="R9" s="19"/>
+      <c r="S9" s="19"/>
+      <c r="T9" s="22"/>
+      <c r="U9" s="49">
         <v>233</v>
       </c>
-      <c r="V9" s="36"/>
-      <c r="W9" s="36"/>
-      <c r="X9" s="36"/>
-      <c r="Y9" s="36"/>
-      <c r="Z9" s="41"/>
+      <c r="V9" s="19"/>
+      <c r="W9" s="19"/>
+      <c r="X9" s="19"/>
+      <c r="Y9" s="19"/>
+      <c r="Z9" s="22"/>
     </row>
     <row r="10" spans="1:26" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="25"/>
-      <c r="B10" s="33" t="s">
+      <c r="A10" s="37"/>
+      <c r="B10" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="40">
+      <c r="C10" s="42">
         <v>7</v>
       </c>
-      <c r="D10" s="36"/>
-      <c r="E10" s="36"/>
-      <c r="F10" s="36"/>
-      <c r="G10" s="36"/>
-      <c r="H10" s="41"/>
-      <c r="I10" s="40">
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="22"/>
+      <c r="I10" s="42">
         <v>3</v>
       </c>
-      <c r="J10" s="36"/>
-      <c r="K10" s="36"/>
-      <c r="L10" s="36"/>
-      <c r="M10" s="36"/>
-      <c r="N10" s="41"/>
-      <c r="O10" s="46">
+      <c r="J10" s="19"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="19"/>
+      <c r="M10" s="19"/>
+      <c r="N10" s="22"/>
+      <c r="O10" s="49">
         <v>3754</v>
       </c>
-      <c r="P10" s="36"/>
-      <c r="Q10" s="36"/>
-      <c r="R10" s="36"/>
-      <c r="S10" s="36"/>
-      <c r="T10" s="41"/>
-      <c r="U10" s="46">
+      <c r="P10" s="19"/>
+      <c r="Q10" s="19"/>
+      <c r="R10" s="19"/>
+      <c r="S10" s="19"/>
+      <c r="T10" s="22"/>
+      <c r="U10" s="49">
         <v>20</v>
       </c>
-      <c r="V10" s="36"/>
-      <c r="W10" s="36"/>
-      <c r="X10" s="36"/>
-      <c r="Y10" s="36"/>
-      <c r="Z10" s="41"/>
+      <c r="V10" s="19"/>
+      <c r="W10" s="19"/>
+      <c r="X10" s="19"/>
+      <c r="Y10" s="19"/>
+      <c r="Z10" s="22"/>
     </row>
     <row r="11" spans="1:26" s="1" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="26"/>
-      <c r="B11" s="34" t="s">
+      <c r="A11" s="38"/>
+      <c r="B11" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="40">
+      <c r="C11" s="42">
         <v>2</v>
       </c>
-      <c r="D11" s="36"/>
-      <c r="E11" s="36"/>
-      <c r="F11" s="36"/>
-      <c r="G11" s="36"/>
-      <c r="H11" s="41"/>
-      <c r="I11" s="40">
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="22"/>
+      <c r="I11" s="42">
         <v>1</v>
       </c>
-      <c r="J11" s="36"/>
-      <c r="K11" s="36"/>
-      <c r="L11" s="36"/>
-      <c r="M11" s="36"/>
-      <c r="N11" s="41"/>
-      <c r="O11" s="46">
+      <c r="J11" s="19"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="19"/>
+      <c r="M11" s="19"/>
+      <c r="N11" s="22"/>
+      <c r="O11" s="49">
         <v>0</v>
       </c>
-      <c r="P11" s="36"/>
-      <c r="Q11" s="36"/>
-      <c r="R11" s="36"/>
-      <c r="S11" s="36"/>
-      <c r="T11" s="41"/>
-      <c r="U11" s="46">
+      <c r="P11" s="19"/>
+      <c r="Q11" s="19"/>
+      <c r="R11" s="19"/>
+      <c r="S11" s="19"/>
+      <c r="T11" s="22"/>
+      <c r="U11" s="49">
         <v>0</v>
       </c>
-      <c r="V11" s="36"/>
-      <c r="W11" s="36"/>
-      <c r="X11" s="36"/>
-      <c r="Y11" s="36"/>
-      <c r="Z11" s="41"/>
+      <c r="V11" s="19"/>
+      <c r="W11" s="19"/>
+      <c r="X11" s="19"/>
+      <c r="Y11" s="19"/>
+      <c r="Z11" s="22"/>
     </row>
     <row r="12" spans="1:26" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="24" t="s">
+      <c r="A12" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="35" t="s">
+      <c r="B12" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="40">
+      <c r="C12" s="42">
         <v>5</v>
       </c>
-      <c r="D12" s="36"/>
-      <c r="E12" s="36"/>
-      <c r="F12" s="36"/>
-      <c r="G12" s="36"/>
-      <c r="H12" s="41"/>
-      <c r="I12" s="40">
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="22"/>
+      <c r="I12" s="42">
         <v>5</v>
       </c>
-      <c r="J12" s="36"/>
-      <c r="K12" s="36"/>
-      <c r="L12" s="36"/>
-      <c r="M12" s="36"/>
-      <c r="N12" s="41"/>
-      <c r="O12" s="46">
+      <c r="J12" s="19"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
+      <c r="M12" s="19"/>
+      <c r="N12" s="22"/>
+      <c r="O12" s="49">
         <v>94</v>
       </c>
-      <c r="P12" s="36"/>
-      <c r="Q12" s="36"/>
-      <c r="R12" s="36"/>
-      <c r="S12" s="36"/>
-      <c r="T12" s="41"/>
-      <c r="U12" s="46">
+      <c r="P12" s="19"/>
+      <c r="Q12" s="19"/>
+      <c r="R12" s="19"/>
+      <c r="S12" s="19"/>
+      <c r="T12" s="22"/>
+      <c r="U12" s="49">
         <v>109</v>
       </c>
-      <c r="V12" s="36"/>
-      <c r="W12" s="36"/>
-      <c r="X12" s="36"/>
-      <c r="Y12" s="36"/>
-      <c r="Z12" s="41"/>
+      <c r="V12" s="19"/>
+      <c r="W12" s="19"/>
+      <c r="X12" s="19"/>
+      <c r="Y12" s="19"/>
+      <c r="Z12" s="22"/>
     </row>
     <row r="13" spans="1:26" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="25"/>
-      <c r="B13" s="33" t="s">
+      <c r="A13" s="37"/>
+      <c r="B13" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="40">
+      <c r="C13" s="42">
         <v>4</v>
       </c>
-      <c r="D13" s="36"/>
-      <c r="E13" s="36"/>
-      <c r="F13" s="36"/>
-      <c r="G13" s="36"/>
-      <c r="H13" s="41"/>
-      <c r="I13" s="40">
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="22"/>
+      <c r="I13" s="42">
         <v>3</v>
       </c>
-      <c r="J13" s="36"/>
-      <c r="K13" s="36"/>
-      <c r="L13" s="36"/>
-      <c r="M13" s="36"/>
-      <c r="N13" s="41"/>
-      <c r="O13" s="46">
+      <c r="J13" s="19"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="19"/>
+      <c r="M13" s="19"/>
+      <c r="N13" s="22"/>
+      <c r="O13" s="49">
         <v>1912</v>
       </c>
-      <c r="P13" s="36"/>
-      <c r="Q13" s="36"/>
-      <c r="R13" s="36"/>
-      <c r="S13" s="36"/>
-      <c r="T13" s="41"/>
-      <c r="U13" s="46">
+      <c r="P13" s="19"/>
+      <c r="Q13" s="19"/>
+      <c r="R13" s="19"/>
+      <c r="S13" s="19"/>
+      <c r="T13" s="22"/>
+      <c r="U13" s="49">
         <v>156</v>
       </c>
-      <c r="V13" s="36"/>
-      <c r="W13" s="36"/>
-      <c r="X13" s="36"/>
-      <c r="Y13" s="36"/>
-      <c r="Z13" s="41"/>
+      <c r="V13" s="19"/>
+      <c r="W13" s="19"/>
+      <c r="X13" s="19"/>
+      <c r="Y13" s="19"/>
+      <c r="Z13" s="22"/>
     </row>
     <row r="14" spans="1:26" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="25"/>
-      <c r="B14" s="33" t="s">
+      <c r="A14" s="37"/>
+      <c r="B14" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="40">
+      <c r="C14" s="42">
         <v>1</v>
       </c>
-      <c r="D14" s="36"/>
-      <c r="E14" s="36"/>
-      <c r="F14" s="36"/>
-      <c r="G14" s="36"/>
-      <c r="H14" s="41"/>
-      <c r="I14" s="40">
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="22"/>
+      <c r="I14" s="42">
         <v>2</v>
       </c>
-      <c r="J14" s="36"/>
-      <c r="K14" s="36"/>
-      <c r="L14" s="36"/>
-      <c r="M14" s="36"/>
-      <c r="N14" s="41"/>
-      <c r="O14" s="46">
+      <c r="J14" s="19"/>
+      <c r="K14" s="19"/>
+      <c r="L14" s="19"/>
+      <c r="M14" s="19"/>
+      <c r="N14" s="22"/>
+      <c r="O14" s="49">
         <v>0</v>
       </c>
-      <c r="P14" s="36"/>
-      <c r="Q14" s="36"/>
-      <c r="R14" s="36"/>
-      <c r="S14" s="36"/>
-      <c r="T14" s="41"/>
-      <c r="U14" s="46">
+      <c r="P14" s="19"/>
+      <c r="Q14" s="19"/>
+      <c r="R14" s="19"/>
+      <c r="S14" s="19"/>
+      <c r="T14" s="22"/>
+      <c r="U14" s="49">
         <v>0</v>
       </c>
-      <c r="V14" s="36"/>
-      <c r="W14" s="36"/>
-      <c r="X14" s="36"/>
-      <c r="Y14" s="36"/>
-      <c r="Z14" s="41"/>
+      <c r="V14" s="19"/>
+      <c r="W14" s="19"/>
+      <c r="X14" s="19"/>
+      <c r="Y14" s="19"/>
+      <c r="Z14" s="22"/>
     </row>
     <row r="15" spans="1:26" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="25"/>
-      <c r="B15" s="33" t="s">
+      <c r="A15" s="37"/>
+      <c r="B15" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="40">
+      <c r="C15" s="42">
         <v>2</v>
       </c>
-      <c r="D15" s="36"/>
-      <c r="E15" s="36"/>
-      <c r="F15" s="36"/>
-      <c r="G15" s="36"/>
-      <c r="H15" s="41"/>
-      <c r="I15" s="40">
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="22"/>
+      <c r="I15" s="42">
         <v>8</v>
       </c>
-      <c r="J15" s="36"/>
-      <c r="K15" s="36"/>
-      <c r="L15" s="36"/>
-      <c r="M15" s="36"/>
-      <c r="N15" s="41"/>
-      <c r="O15" s="46">
+      <c r="J15" s="19"/>
+      <c r="K15" s="19"/>
+      <c r="L15" s="19"/>
+      <c r="M15" s="19"/>
+      <c r="N15" s="22"/>
+      <c r="O15" s="49">
         <v>130</v>
       </c>
-      <c r="P15" s="36"/>
-      <c r="Q15" s="36"/>
-      <c r="R15" s="36"/>
-      <c r="S15" s="36"/>
-      <c r="T15" s="41"/>
-      <c r="U15" s="46">
+      <c r="P15" s="19"/>
+      <c r="Q15" s="19"/>
+      <c r="R15" s="19"/>
+      <c r="S15" s="19"/>
+      <c r="T15" s="22"/>
+      <c r="U15" s="49">
         <v>15</v>
       </c>
-      <c r="V15" s="36"/>
-      <c r="W15" s="36"/>
-      <c r="X15" s="36"/>
-      <c r="Y15" s="36"/>
-      <c r="Z15" s="41"/>
+      <c r="V15" s="19"/>
+      <c r="W15" s="19"/>
+      <c r="X15" s="19"/>
+      <c r="Y15" s="19"/>
+      <c r="Z15" s="22"/>
     </row>
     <row r="16" spans="1:26" s="1" customFormat="1" ht="13.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="26"/>
-      <c r="B16" s="34" t="s">
+      <c r="A16" s="38"/>
+      <c r="B16" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="42">
+      <c r="C16" s="43">
         <v>5</v>
       </c>
-      <c r="D16" s="43"/>
-      <c r="E16" s="43"/>
-      <c r="F16" s="43"/>
-      <c r="G16" s="43"/>
-      <c r="H16" s="44"/>
-      <c r="I16" s="42">
+      <c r="D16" s="23"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="23"/>
+      <c r="G16" s="23"/>
+      <c r="H16" s="24"/>
+      <c r="I16" s="43">
         <v>3</v>
       </c>
-      <c r="J16" s="43"/>
-      <c r="K16" s="43"/>
-      <c r="L16" s="43"/>
-      <c r="M16" s="43"/>
-      <c r="N16" s="44"/>
-      <c r="O16" s="47">
+      <c r="J16" s="23"/>
+      <c r="K16" s="23"/>
+      <c r="L16" s="23"/>
+      <c r="M16" s="23"/>
+      <c r="N16" s="24"/>
+      <c r="O16" s="50">
         <v>1007</v>
       </c>
-      <c r="P16" s="43"/>
-      <c r="Q16" s="43"/>
-      <c r="R16" s="43"/>
-      <c r="S16" s="43"/>
-      <c r="T16" s="44"/>
-      <c r="U16" s="47">
+      <c r="P16" s="23"/>
+      <c r="Q16" s="23"/>
+      <c r="R16" s="23"/>
+      <c r="S16" s="23"/>
+      <c r="T16" s="24"/>
+      <c r="U16" s="50">
         <v>81</v>
       </c>
-      <c r="V16" s="43"/>
-      <c r="W16" s="43"/>
-      <c r="X16" s="43"/>
-      <c r="Y16" s="43"/>
-      <c r="Z16" s="44"/>
+      <c r="V16" s="23"/>
+      <c r="W16" s="23"/>
+      <c r="X16" s="23"/>
+      <c r="Y16" s="23"/>
+      <c r="Z16" s="24"/>
     </row>
     <row r="17" spans="1:26" s="2" customFormat="1" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="23"/>
-      <c r="B17" s="50" t="s">
+      <c r="A17" s="40"/>
+      <c r="B17" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17" s="44">
         <v>150</v>
       </c>
-      <c r="D17" s="28"/>
-      <c r="E17" s="28"/>
-      <c r="F17" s="28"/>
-      <c r="G17" s="28"/>
-      <c r="H17" s="28"/>
-      <c r="I17" s="27">
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="46">
         <v>60</v>
       </c>
-      <c r="J17" s="28"/>
-      <c r="K17" s="28"/>
-      <c r="L17" s="28"/>
-      <c r="M17" s="28"/>
-      <c r="N17" s="28"/>
-      <c r="O17" s="9">
+      <c r="J17" s="12"/>
+      <c r="K17" s="12"/>
+      <c r="L17" s="12"/>
+      <c r="M17" s="12"/>
+      <c r="N17" s="12"/>
+      <c r="O17" s="51">
         <v>12000</v>
       </c>
-      <c r="P17" s="28"/>
-      <c r="Q17" s="28"/>
-      <c r="R17" s="28"/>
-      <c r="S17" s="28"/>
-      <c r="T17" s="28"/>
-      <c r="U17" s="9">
+      <c r="P17" s="12"/>
+      <c r="Q17" s="12"/>
+      <c r="R17" s="12"/>
+      <c r="S17" s="12"/>
+      <c r="T17" s="12"/>
+      <c r="U17" s="51">
         <v>150</v>
       </c>
-      <c r="V17" s="28"/>
-      <c r="W17" s="28"/>
-      <c r="X17" s="28"/>
-      <c r="Y17" s="28"/>
-      <c r="Z17" s="29"/>
+      <c r="V17" s="12"/>
+      <c r="W17" s="12"/>
+      <c r="X17" s="12"/>
+      <c r="Y17" s="12"/>
+      <c r="Z17" s="13"/>
     </row>
     <row r="18" spans="1:26" s="2" customFormat="1" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="23"/>
-      <c r="B18" s="51" t="s">
+      <c r="A18" s="40"/>
+      <c r="B18" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C18" s="44">
         <f>SUM(C4:C16)</f>
         <v>113</v>
       </c>
-      <c r="D18" s="28"/>
-      <c r="E18" s="28"/>
-      <c r="F18" s="28"/>
-      <c r="G18" s="28"/>
-      <c r="H18" s="28"/>
-      <c r="I18" s="27">
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="46">
         <f>SUM(I4:I16)</f>
         <v>103</v>
       </c>
-      <c r="J18" s="28"/>
-      <c r="K18" s="28"/>
-      <c r="L18" s="28"/>
-      <c r="M18" s="28"/>
-      <c r="N18" s="28"/>
-      <c r="O18" s="9">
+      <c r="J18" s="12"/>
+      <c r="K18" s="12"/>
+      <c r="L18" s="12"/>
+      <c r="M18" s="12"/>
+      <c r="N18" s="12"/>
+      <c r="O18" s="51">
         <f>SUM(O4:O16)</f>
         <v>12612</v>
       </c>
-      <c r="P18" s="28"/>
-      <c r="Q18" s="28"/>
-      <c r="R18" s="28"/>
-      <c r="S18" s="28"/>
-      <c r="T18" s="28"/>
-      <c r="U18" s="9">
+      <c r="P18" s="12"/>
+      <c r="Q18" s="12"/>
+      <c r="R18" s="12"/>
+      <c r="S18" s="12"/>
+      <c r="T18" s="12"/>
+      <c r="U18" s="51">
         <f>SUM(U4:U16)</f>
         <v>1444</v>
       </c>
-      <c r="V18" s="28"/>
-      <c r="W18" s="28"/>
-      <c r="X18" s="28"/>
-      <c r="Y18" s="28"/>
-      <c r="Z18" s="29"/>
+      <c r="V18" s="12"/>
+      <c r="W18" s="12"/>
+      <c r="X18" s="12"/>
+      <c r="Y18" s="12"/>
+      <c r="Z18" s="13"/>
     </row>
     <row r="19" spans="1:26" s="2" customFormat="1" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="23"/>
-      <c r="B19" s="52" t="s">
+      <c r="A19" s="40"/>
+      <c r="B19" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="45">
         <v>11.538461538461538</v>
       </c>
-      <c r="D19" s="30"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="30"/>
-      <c r="H19" s="30"/>
-      <c r="I19" s="31">
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="14"/>
+      <c r="H19" s="14"/>
+      <c r="I19" s="47">
         <v>4.615384615384615</v>
       </c>
-      <c r="J19" s="30"/>
-      <c r="K19" s="30"/>
-      <c r="L19" s="30"/>
-      <c r="M19" s="30"/>
-      <c r="N19" s="30"/>
-      <c r="O19" s="10">
+      <c r="J19" s="14"/>
+      <c r="K19" s="14"/>
+      <c r="L19" s="14"/>
+      <c r="M19" s="14"/>
+      <c r="N19" s="14"/>
+      <c r="O19" s="52">
         <v>923.07692307692309</v>
       </c>
-      <c r="P19" s="30"/>
-      <c r="Q19" s="30"/>
-      <c r="R19" s="30"/>
-      <c r="S19" s="30"/>
-      <c r="T19" s="30"/>
-      <c r="U19" s="10">
+      <c r="P19" s="14"/>
+      <c r="Q19" s="14"/>
+      <c r="R19" s="14"/>
+      <c r="S19" s="14"/>
+      <c r="T19" s="14"/>
+      <c r="U19" s="52">
         <v>11.538461538461538</v>
       </c>
-      <c r="V19" s="30"/>
-      <c r="W19" s="30"/>
-      <c r="X19" s="30"/>
-      <c r="Y19" s="30"/>
-      <c r="Z19" s="32"/>
+      <c r="V19" s="14"/>
+      <c r="W19" s="14"/>
+      <c r="X19" s="14"/>
+      <c r="Y19" s="14"/>
+      <c r="Z19" s="15"/>
     </row>
     <row r="20" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A20" s="23"/>
+      <c r="A20" s="40"/>
     </row>
     <row r="29" spans="1:26" x14ac:dyDescent="0.3">
       <c r="D29" s="5" t="s">
@@ -1777,17 +1782,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A16"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A17:A20"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C1:Z1"/>
     <mergeCell ref="C2:H2"/>
     <mergeCell ref="I2:N2"/>
     <mergeCell ref="O2:T2"/>
     <mergeCell ref="U2:Z2"/>
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="A12:A16"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A17:A20"/>
   </mergeCells>
   <conditionalFormatting sqref="C4:C16">
     <cfRule type="colorScale" priority="44">

--- a/data/Heat map 4-1 Capacity Building.xlsx
+++ b/data/Heat map 4-1 Capacity Building.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8705F90E-0B78-4D0E-A361-82055CC6C799}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{503DD465-B0DF-421E-9B45-009FCB29DD29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{60C6FB9E-1B92-4818-B8F8-C10D82D4AFAC}"/>
   </bookViews>
@@ -139,11 +139,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="168" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -540,7 +541,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -619,6 +620,42 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -658,40 +695,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="3" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="3" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1013,74 +1017,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" s="2" customFormat="1" ht="15.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C1" s="30" t="s">
+      <c r="C1" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="31"/>
-      <c r="R1" s="31"/>
-      <c r="S1" s="31"/>
-      <c r="T1" s="31"/>
-      <c r="U1" s="31"/>
-      <c r="V1" s="31"/>
-      <c r="W1" s="31"/>
-      <c r="X1" s="31"/>
-      <c r="Y1" s="31"/>
-      <c r="Z1" s="32"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="43"/>
+      <c r="O1" s="43"/>
+      <c r="P1" s="43"/>
+      <c r="Q1" s="43"/>
+      <c r="R1" s="43"/>
+      <c r="S1" s="43"/>
+      <c r="T1" s="43"/>
+      <c r="U1" s="43"/>
+      <c r="V1" s="43"/>
+      <c r="W1" s="43"/>
+      <c r="X1" s="43"/>
+      <c r="Y1" s="43"/>
+      <c r="Z1" s="44"/>
     </row>
     <row r="2" spans="1:26" s="6" customFormat="1" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="39"/>
-      <c r="B2" s="28" t="s">
+      <c r="A2" s="51"/>
+      <c r="B2" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="33" t="s">
+      <c r="C2" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="33" t="s">
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="45" t="s">
         <v>27</v>
       </c>
-      <c r="J2" s="34"/>
-      <c r="K2" s="34"/>
-      <c r="L2" s="34"/>
-      <c r="M2" s="34"/>
-      <c r="N2" s="35"/>
-      <c r="O2" s="33" t="s">
+      <c r="J2" s="46"/>
+      <c r="K2" s="46"/>
+      <c r="L2" s="46"/>
+      <c r="M2" s="46"/>
+      <c r="N2" s="47"/>
+      <c r="O2" s="45" t="s">
         <v>23</v>
       </c>
-      <c r="P2" s="34"/>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="34"/>
-      <c r="T2" s="35"/>
-      <c r="U2" s="33" t="s">
+      <c r="P2" s="46"/>
+      <c r="Q2" s="46"/>
+      <c r="R2" s="46"/>
+      <c r="S2" s="46"/>
+      <c r="T2" s="47"/>
+      <c r="U2" s="45" t="s">
         <v>28</v>
       </c>
-      <c r="V2" s="34"/>
-      <c r="W2" s="34"/>
-      <c r="X2" s="34"/>
-      <c r="Y2" s="34"/>
-      <c r="Z2" s="35"/>
+      <c r="V2" s="46"/>
+      <c r="W2" s="46"/>
+      <c r="X2" s="46"/>
+      <c r="Y2" s="46"/>
+      <c r="Z2" s="47"/>
     </row>
     <row r="3" spans="1:26" s="1" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="39"/>
-      <c r="B3" s="29"/>
+      <c r="A3" s="51"/>
+      <c r="B3" s="41"/>
       <c r="C3" s="10" t="s">
         <v>0</v>
       </c>
@@ -1155,13 +1159,13 @@
       </c>
     </row>
     <row r="4" spans="1:26" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="48" t="s">
         <v>12</v>
       </c>
       <c r="B4" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="41">
+      <c r="C4" s="28">
         <v>1</v>
       </c>
       <c r="D4" s="20"/>
@@ -1169,7 +1173,7 @@
       <c r="F4" s="20"/>
       <c r="G4" s="20"/>
       <c r="H4" s="21"/>
-      <c r="I4" s="41">
+      <c r="I4" s="28">
         <v>1</v>
       </c>
       <c r="J4" s="20"/>
@@ -1177,7 +1181,7 @@
       <c r="L4" s="20"/>
       <c r="M4" s="20"/>
       <c r="N4" s="21"/>
-      <c r="O4" s="48">
+      <c r="O4" s="35">
         <v>68</v>
       </c>
       <c r="P4" s="20"/>
@@ -1185,7 +1189,7 @@
       <c r="R4" s="20"/>
       <c r="S4" s="20"/>
       <c r="T4" s="21"/>
-      <c r="U4" s="48">
+      <c r="U4" s="35">
         <v>184</v>
       </c>
       <c r="V4" s="20"/>
@@ -1195,11 +1199,11 @@
       <c r="Z4" s="21"/>
     </row>
     <row r="5" spans="1:26" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="37"/>
+      <c r="A5" s="49"/>
       <c r="B5" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="42">
+      <c r="C5" s="29">
         <v>24</v>
       </c>
       <c r="D5" s="19"/>
@@ -1207,7 +1211,7 @@
       <c r="F5" s="19"/>
       <c r="G5" s="19"/>
       <c r="H5" s="22"/>
-      <c r="I5" s="42">
+      <c r="I5" s="29">
         <v>28</v>
       </c>
       <c r="J5" s="19"/>
@@ -1215,7 +1219,7 @@
       <c r="L5" s="19"/>
       <c r="M5" s="19"/>
       <c r="N5" s="22"/>
-      <c r="O5" s="49">
+      <c r="O5" s="36">
         <v>108</v>
       </c>
       <c r="P5" s="19"/>
@@ -1223,7 +1227,7 @@
       <c r="R5" s="19"/>
       <c r="S5" s="19"/>
       <c r="T5" s="22"/>
-      <c r="U5" s="49">
+      <c r="U5" s="36">
         <v>214</v>
       </c>
       <c r="V5" s="19"/>
@@ -1233,11 +1237,11 @@
       <c r="Z5" s="22"/>
     </row>
     <row r="6" spans="1:26" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="37"/>
+      <c r="A6" s="49"/>
       <c r="B6" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="42">
+      <c r="C6" s="29">
         <v>26</v>
       </c>
       <c r="D6" s="19"/>
@@ -1245,7 +1249,7 @@
       <c r="F6" s="19"/>
       <c r="G6" s="19"/>
       <c r="H6" s="22"/>
-      <c r="I6" s="42">
+      <c r="I6" s="29">
         <v>19</v>
       </c>
       <c r="J6" s="19"/>
@@ -1253,7 +1257,7 @@
       <c r="L6" s="19"/>
       <c r="M6" s="19"/>
       <c r="N6" s="22"/>
-      <c r="O6" s="49">
+      <c r="O6" s="36">
         <v>5</v>
       </c>
       <c r="P6" s="19"/>
@@ -1261,7 +1265,7 @@
       <c r="R6" s="19"/>
       <c r="S6" s="19"/>
       <c r="T6" s="22"/>
-      <c r="U6" s="49">
+      <c r="U6" s="36">
         <v>113</v>
       </c>
       <c r="V6" s="19"/>
@@ -1271,11 +1275,11 @@
       <c r="Z6" s="22"/>
     </row>
     <row r="7" spans="1:26" s="1" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="38"/>
+      <c r="A7" s="50"/>
       <c r="B7" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="42">
+      <c r="C7" s="29">
         <v>5</v>
       </c>
       <c r="D7" s="19"/>
@@ -1283,7 +1287,7 @@
       <c r="F7" s="19"/>
       <c r="G7" s="19"/>
       <c r="H7" s="22"/>
-      <c r="I7" s="42">
+      <c r="I7" s="29">
         <v>7</v>
       </c>
       <c r="J7" s="19"/>
@@ -1291,7 +1295,7 @@
       <c r="L7" s="19"/>
       <c r="M7" s="19"/>
       <c r="N7" s="22"/>
-      <c r="O7" s="49">
+      <c r="O7" s="36">
         <v>2247</v>
       </c>
       <c r="P7" s="19"/>
@@ -1299,7 +1303,7 @@
       <c r="R7" s="19"/>
       <c r="S7" s="19"/>
       <c r="T7" s="22"/>
-      <c r="U7" s="49">
+      <c r="U7" s="36">
         <v>309</v>
       </c>
       <c r="V7" s="19"/>
@@ -1309,13 +1313,13 @@
       <c r="Z7" s="22"/>
     </row>
     <row r="8" spans="1:26" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="36" t="s">
+      <c r="A8" s="48" t="s">
         <v>13</v>
       </c>
       <c r="B8" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="42">
+      <c r="C8" s="29">
         <v>9</v>
       </c>
       <c r="D8" s="19"/>
@@ -1323,7 +1327,7 @@
       <c r="F8" s="19"/>
       <c r="G8" s="19"/>
       <c r="H8" s="22"/>
-      <c r="I8" s="42">
+      <c r="I8" s="29">
         <v>9</v>
       </c>
       <c r="J8" s="19"/>
@@ -1331,7 +1335,7 @@
       <c r="L8" s="19"/>
       <c r="M8" s="19"/>
       <c r="N8" s="22"/>
-      <c r="O8" s="49">
+      <c r="O8" s="36">
         <v>102</v>
       </c>
       <c r="P8" s="19"/>
@@ -1339,7 +1343,7 @@
       <c r="R8" s="19"/>
       <c r="S8" s="19"/>
       <c r="T8" s="22"/>
-      <c r="U8" s="49">
+      <c r="U8" s="36">
         <v>10</v>
       </c>
       <c r="V8" s="19"/>
@@ -1349,11 +1353,11 @@
       <c r="Z8" s="22"/>
     </row>
     <row r="9" spans="1:26" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="37"/>
+      <c r="A9" s="49"/>
       <c r="B9" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="42">
+      <c r="C9" s="29">
         <v>22</v>
       </c>
       <c r="D9" s="19"/>
@@ -1361,7 +1365,7 @@
       <c r="F9" s="19"/>
       <c r="G9" s="19"/>
       <c r="H9" s="22"/>
-      <c r="I9" s="42">
+      <c r="I9" s="29">
         <v>14</v>
       </c>
       <c r="J9" s="19"/>
@@ -1369,7 +1373,7 @@
       <c r="L9" s="19"/>
       <c r="M9" s="19"/>
       <c r="N9" s="22"/>
-      <c r="O9" s="49">
+      <c r="O9" s="36">
         <v>3185</v>
       </c>
       <c r="P9" s="19"/>
@@ -1377,7 +1381,7 @@
       <c r="R9" s="19"/>
       <c r="S9" s="19"/>
       <c r="T9" s="22"/>
-      <c r="U9" s="49">
+      <c r="U9" s="36">
         <v>233</v>
       </c>
       <c r="V9" s="19"/>
@@ -1387,11 +1391,11 @@
       <c r="Z9" s="22"/>
     </row>
     <row r="10" spans="1:26" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="37"/>
+      <c r="A10" s="49"/>
       <c r="B10" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="42">
+      <c r="C10" s="29">
         <v>7</v>
       </c>
       <c r="D10" s="19"/>
@@ -1399,7 +1403,7 @@
       <c r="F10" s="19"/>
       <c r="G10" s="19"/>
       <c r="H10" s="22"/>
-      <c r="I10" s="42">
+      <c r="I10" s="29">
         <v>3</v>
       </c>
       <c r="J10" s="19"/>
@@ -1407,7 +1411,7 @@
       <c r="L10" s="19"/>
       <c r="M10" s="19"/>
       <c r="N10" s="22"/>
-      <c r="O10" s="49">
+      <c r="O10" s="36">
         <v>3754</v>
       </c>
       <c r="P10" s="19"/>
@@ -1415,7 +1419,7 @@
       <c r="R10" s="19"/>
       <c r="S10" s="19"/>
       <c r="T10" s="22"/>
-      <c r="U10" s="49">
+      <c r="U10" s="36">
         <v>20</v>
       </c>
       <c r="V10" s="19"/>
@@ -1425,11 +1429,11 @@
       <c r="Z10" s="22"/>
     </row>
     <row r="11" spans="1:26" s="1" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="38"/>
+      <c r="A11" s="50"/>
       <c r="B11" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="42">
+      <c r="C11" s="29">
         <v>2</v>
       </c>
       <c r="D11" s="19"/>
@@ -1437,7 +1441,7 @@
       <c r="F11" s="19"/>
       <c r="G11" s="19"/>
       <c r="H11" s="22"/>
-      <c r="I11" s="42">
+      <c r="I11" s="29">
         <v>1</v>
       </c>
       <c r="J11" s="19"/>
@@ -1445,7 +1449,7 @@
       <c r="L11" s="19"/>
       <c r="M11" s="19"/>
       <c r="N11" s="22"/>
-      <c r="O11" s="49">
+      <c r="O11" s="53">
         <v>0</v>
       </c>
       <c r="P11" s="19"/>
@@ -1453,7 +1457,7 @@
       <c r="R11" s="19"/>
       <c r="S11" s="19"/>
       <c r="T11" s="22"/>
-      <c r="U11" s="49">
+      <c r="U11" s="53">
         <v>0</v>
       </c>
       <c r="V11" s="19"/>
@@ -1463,13 +1467,13 @@
       <c r="Z11" s="22"/>
     </row>
     <row r="12" spans="1:26" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="36" t="s">
+      <c r="A12" s="48" t="s">
         <v>14</v>
       </c>
       <c r="B12" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="42">
+      <c r="C12" s="29">
         <v>5</v>
       </c>
       <c r="D12" s="19"/>
@@ -1477,7 +1481,7 @@
       <c r="F12" s="19"/>
       <c r="G12" s="19"/>
       <c r="H12" s="22"/>
-      <c r="I12" s="42">
+      <c r="I12" s="29">
         <v>5</v>
       </c>
       <c r="J12" s="19"/>
@@ -1485,7 +1489,7 @@
       <c r="L12" s="19"/>
       <c r="M12" s="19"/>
       <c r="N12" s="22"/>
-      <c r="O12" s="49">
+      <c r="O12" s="36">
         <v>94</v>
       </c>
       <c r="P12" s="19"/>
@@ -1493,7 +1497,7 @@
       <c r="R12" s="19"/>
       <c r="S12" s="19"/>
       <c r="T12" s="22"/>
-      <c r="U12" s="49">
+      <c r="U12" s="36">
         <v>109</v>
       </c>
       <c r="V12" s="19"/>
@@ -1503,11 +1507,11 @@
       <c r="Z12" s="22"/>
     </row>
     <row r="13" spans="1:26" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="37"/>
+      <c r="A13" s="49"/>
       <c r="B13" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="42">
+      <c r="C13" s="29">
         <v>4</v>
       </c>
       <c r="D13" s="19"/>
@@ -1515,7 +1519,7 @@
       <c r="F13" s="19"/>
       <c r="G13" s="19"/>
       <c r="H13" s="22"/>
-      <c r="I13" s="42">
+      <c r="I13" s="29">
         <v>3</v>
       </c>
       <c r="J13" s="19"/>
@@ -1523,7 +1527,7 @@
       <c r="L13" s="19"/>
       <c r="M13" s="19"/>
       <c r="N13" s="22"/>
-      <c r="O13" s="49">
+      <c r="O13" s="36">
         <v>1912</v>
       </c>
       <c r="P13" s="19"/>
@@ -1531,7 +1535,7 @@
       <c r="R13" s="19"/>
       <c r="S13" s="19"/>
       <c r="T13" s="22"/>
-      <c r="U13" s="49">
+      <c r="U13" s="36">
         <v>156</v>
       </c>
       <c r="V13" s="19"/>
@@ -1541,11 +1545,11 @@
       <c r="Z13" s="22"/>
     </row>
     <row r="14" spans="1:26" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="37"/>
+      <c r="A14" s="49"/>
       <c r="B14" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="42">
+      <c r="C14" s="29">
         <v>1</v>
       </c>
       <c r="D14" s="19"/>
@@ -1553,7 +1557,7 @@
       <c r="F14" s="19"/>
       <c r="G14" s="19"/>
       <c r="H14" s="22"/>
-      <c r="I14" s="42">
+      <c r="I14" s="29">
         <v>2</v>
       </c>
       <c r="J14" s="19"/>
@@ -1561,7 +1565,7 @@
       <c r="L14" s="19"/>
       <c r="M14" s="19"/>
       <c r="N14" s="22"/>
-      <c r="O14" s="49">
+      <c r="O14" s="53">
         <v>0</v>
       </c>
       <c r="P14" s="19"/>
@@ -1569,7 +1573,7 @@
       <c r="R14" s="19"/>
       <c r="S14" s="19"/>
       <c r="T14" s="22"/>
-      <c r="U14" s="49">
+      <c r="U14" s="53">
         <v>0</v>
       </c>
       <c r="V14" s="19"/>
@@ -1579,11 +1583,11 @@
       <c r="Z14" s="22"/>
     </row>
     <row r="15" spans="1:26" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="37"/>
+      <c r="A15" s="49"/>
       <c r="B15" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="42">
+      <c r="C15" s="29">
         <v>2</v>
       </c>
       <c r="D15" s="19"/>
@@ -1591,7 +1595,7 @@
       <c r="F15" s="19"/>
       <c r="G15" s="19"/>
       <c r="H15" s="22"/>
-      <c r="I15" s="42">
+      <c r="I15" s="29">
         <v>8</v>
       </c>
       <c r="J15" s="19"/>
@@ -1599,7 +1603,7 @@
       <c r="L15" s="19"/>
       <c r="M15" s="19"/>
       <c r="N15" s="22"/>
-      <c r="O15" s="49">
+      <c r="O15" s="36">
         <v>130</v>
       </c>
       <c r="P15" s="19"/>
@@ -1607,7 +1611,7 @@
       <c r="R15" s="19"/>
       <c r="S15" s="19"/>
       <c r="T15" s="22"/>
-      <c r="U15" s="49">
+      <c r="U15" s="36">
         <v>15</v>
       </c>
       <c r="V15" s="19"/>
@@ -1617,11 +1621,11 @@
       <c r="Z15" s="22"/>
     </row>
     <row r="16" spans="1:26" s="1" customFormat="1" ht="13.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="38"/>
+      <c r="A16" s="50"/>
       <c r="B16" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="43">
+      <c r="C16" s="30">
         <v>5</v>
       </c>
       <c r="D16" s="23"/>
@@ -1629,7 +1633,7 @@
       <c r="F16" s="23"/>
       <c r="G16" s="23"/>
       <c r="H16" s="24"/>
-      <c r="I16" s="43">
+      <c r="I16" s="30">
         <v>3</v>
       </c>
       <c r="J16" s="23"/>
@@ -1637,7 +1641,7 @@
       <c r="L16" s="23"/>
       <c r="M16" s="23"/>
       <c r="N16" s="24"/>
-      <c r="O16" s="50">
+      <c r="O16" s="37">
         <v>1007</v>
       </c>
       <c r="P16" s="23"/>
@@ -1645,7 +1649,7 @@
       <c r="R16" s="23"/>
       <c r="S16" s="23"/>
       <c r="T16" s="24"/>
-      <c r="U16" s="50">
+      <c r="U16" s="37">
         <v>81</v>
       </c>
       <c r="V16" s="23"/>
@@ -1655,11 +1659,11 @@
       <c r="Z16" s="24"/>
     </row>
     <row r="17" spans="1:26" s="2" customFormat="1" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="40"/>
+      <c r="A17" s="52"/>
       <c r="B17" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="C17" s="44">
+      <c r="C17" s="31">
         <v>150</v>
       </c>
       <c r="D17" s="12"/>
@@ -1667,7 +1671,7 @@
       <c r="F17" s="12"/>
       <c r="G17" s="12"/>
       <c r="H17" s="12"/>
-      <c r="I17" s="46">
+      <c r="I17" s="33">
         <v>60</v>
       </c>
       <c r="J17" s="12"/>
@@ -1675,7 +1679,7 @@
       <c r="L17" s="12"/>
       <c r="M17" s="12"/>
       <c r="N17" s="12"/>
-      <c r="O17" s="51">
+      <c r="O17" s="38">
         <v>12000</v>
       </c>
       <c r="P17" s="12"/>
@@ -1683,7 +1687,7 @@
       <c r="R17" s="12"/>
       <c r="S17" s="12"/>
       <c r="T17" s="12"/>
-      <c r="U17" s="51">
+      <c r="U17" s="38">
         <v>150</v>
       </c>
       <c r="V17" s="12"/>
@@ -1693,11 +1697,11 @@
       <c r="Z17" s="13"/>
     </row>
     <row r="18" spans="1:26" s="2" customFormat="1" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="40"/>
+      <c r="A18" s="52"/>
       <c r="B18" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="44">
+      <c r="C18" s="31">
         <f>SUM(C4:C16)</f>
         <v>113</v>
       </c>
@@ -1706,7 +1710,7 @@
       <c r="F18" s="12"/>
       <c r="G18" s="12"/>
       <c r="H18" s="12"/>
-      <c r="I18" s="46">
+      <c r="I18" s="33">
         <f>SUM(I4:I16)</f>
         <v>103</v>
       </c>
@@ -1715,7 +1719,7 @@
       <c r="L18" s="12"/>
       <c r="M18" s="12"/>
       <c r="N18" s="12"/>
-      <c r="O18" s="51">
+      <c r="O18" s="38">
         <f>SUM(O4:O16)</f>
         <v>12612</v>
       </c>
@@ -1724,7 +1728,7 @@
       <c r="R18" s="12"/>
       <c r="S18" s="12"/>
       <c r="T18" s="12"/>
-      <c r="U18" s="51">
+      <c r="U18" s="38">
         <f>SUM(U4:U16)</f>
         <v>1444</v>
       </c>
@@ -1735,11 +1739,11 @@
       <c r="Z18" s="13"/>
     </row>
     <row r="19" spans="1:26" s="2" customFormat="1" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="40"/>
+      <c r="A19" s="52"/>
       <c r="B19" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="45">
+      <c r="C19" s="32">
         <v>11.538461538461538</v>
       </c>
       <c r="D19" s="14"/>
@@ -1747,7 +1751,7 @@
       <c r="F19" s="14"/>
       <c r="G19" s="14"/>
       <c r="H19" s="14"/>
-      <c r="I19" s="47">
+      <c r="I19" s="34">
         <v>4.615384615384615</v>
       </c>
       <c r="J19" s="14"/>
@@ -1755,7 +1759,7 @@
       <c r="L19" s="14"/>
       <c r="M19" s="14"/>
       <c r="N19" s="14"/>
-      <c r="O19" s="52">
+      <c r="O19" s="39">
         <v>923.07692307692309</v>
       </c>
       <c r="P19" s="14"/>
@@ -1763,7 +1767,7 @@
       <c r="R19" s="14"/>
       <c r="S19" s="14"/>
       <c r="T19" s="14"/>
-      <c r="U19" s="52">
+      <c r="U19" s="39">
         <v>11.538461538461538</v>
       </c>
       <c r="V19" s="14"/>
@@ -1773,7 +1777,7 @@
       <c r="Z19" s="15"/>
     </row>
     <row r="20" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A20" s="40"/>
+      <c r="A20" s="52"/>
     </row>
     <row r="29" spans="1:26" x14ac:dyDescent="0.3">
       <c r="D29" s="5" t="s">
@@ -1795,7 +1799,7 @@
     <mergeCell ref="U2:Z2"/>
   </mergeCells>
   <conditionalFormatting sqref="C4:C16">
-    <cfRule type="colorScale" priority="44">
+    <cfRule type="colorScale" priority="46">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$C$19/2"/>
@@ -1807,7 +1811,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I4:I16">
-    <cfRule type="colorScale" priority="45">
+    <cfRule type="colorScale" priority="47">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$I$19/2"/>
@@ -1819,7 +1823,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O4:O16">
-    <cfRule type="colorScale" priority="46">
+    <cfRule type="colorScale" priority="48">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$O$19/2"/>
@@ -1830,12 +1834,36 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U4:U16">
-    <cfRule type="colorScale" priority="47">
+  <conditionalFormatting sqref="U4:U10 U12:U13 U15:U16">
+    <cfRule type="colorScale" priority="49">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$U$19/2"/>
         <cfvo type="formula" val="$U$19"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U11">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="formula" val="$O$19/2"/>
+        <cfvo type="formula" val="$O$19"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U14">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="formula" val="$O$19/2"/>
+        <cfvo type="formula" val="$O$19"/>
         <color rgb="FFFF0000"/>
         <color rgb="FFFFFF00"/>
         <color rgb="FF00B050"/>
